--- a/ploy/resources/sample/MiningAchievement.xlsx
+++ b/ploy/resources/sample/MiningAchievement.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\ploygame\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -430,13 +430,13 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
-      <name val="微软雅黑"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1540,7 +1540,7 @@
         <v>17</v>
       </c>
       <c r="F5">
-        <v>400800057</v>
+        <v>400800066</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -1563,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="F6">
-        <v>400800058</v>
+        <v>400800067</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
@@ -1586,7 +1586,7 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>400800059</v>
+        <v>400800068</v>
       </c>
       <c r="G7" t="s">
         <v>26</v>
@@ -1609,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="F8">
-        <v>400800058</v>
+        <v>400800069</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -1632,7 +1632,7 @@
         <v>33</v>
       </c>
       <c r="F9">
-        <v>400800060</v>
+        <v>400800070</v>
       </c>
       <c r="G9" t="s">
         <v>34</v>
